--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N86_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N86_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.39474638976574</v>
+        <v>5.914146288336934</v>
       </c>
       <c r="D2" t="n">
-        <v>38.31593324449554</v>
+        <v>6.226339152230525</v>
       </c>
       <c r="E2" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F2" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.09648943430713</v>
+        <v>2.128179533074908</v>
       </c>
       <c r="D3" t="n">
-        <v>14.35389902719232</v>
+        <v>2.332508591918752</v>
       </c>
       <c r="E3" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F3" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.69426038535175</v>
+        <v>6.77531731261966</v>
       </c>
       <c r="D4" t="n">
-        <v>43.36821207933936</v>
+        <v>7.047334462892646</v>
       </c>
       <c r="E4" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F4" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.18758282271232</v>
+        <v>3.442982208690751</v>
       </c>
       <c r="D5" t="n">
-        <v>20.42208740407388</v>
+        <v>3.318589203162005</v>
       </c>
       <c r="E5" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F5" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.04077570640096</v>
+        <v>5.856626052290157</v>
       </c>
       <c r="D6" t="n">
-        <v>36.68025309020489</v>
+        <v>5.960541127158294</v>
       </c>
       <c r="E6" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F6" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.15051869097524</v>
+        <v>3.111959287283476</v>
       </c>
       <c r="D7" t="n">
-        <v>19.24342268750144</v>
+        <v>3.127056186718983</v>
       </c>
       <c r="E7" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F7" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.52803974210411</v>
+        <v>4.310806458091919</v>
       </c>
       <c r="D8" t="n">
-        <v>27.69969257949246</v>
+        <v>4.501200044167526</v>
       </c>
       <c r="E8" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F8" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.00735135169495</v>
+        <v>2.763694594650429</v>
       </c>
       <c r="D9" t="n">
-        <v>27.700612295414</v>
+        <v>4.501349498004775</v>
       </c>
       <c r="E9" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F9" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.39680323716919</v>
+        <v>5.914480526039994</v>
       </c>
       <c r="D10" t="n">
-        <v>41.50429189028416</v>
+        <v>6.744447432171176</v>
       </c>
       <c r="E10" t="n">
-        <v>9.779533306236237</v>
+        <v>1.589174162263389</v>
       </c>
       <c r="F10" t="n">
-        <v>9.930880731233712</v>
+        <v>1.613768118825478</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
